--- a/basedatos_partidas/salida/descompuestos/CT-12-07-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-12-07-020.xlsx
@@ -591,10 +591,10 @@
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="H12" t="n">
-        <v>6.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="13">
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="H14" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="15">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>75.2</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="16">
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>99.8</v>
+        <v>100.9</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>100.8</v>
+        <v>101.91</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-12-07-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-12-07-020.xlsx
@@ -565,10 +565,10 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -617,10 +617,10 @@
         <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="H13" t="n">
-        <v>8.4</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="14">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>76.3</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>100.9</v>
+        <v>121.7</v>
       </c>
       <c r="H25" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>101.91</v>
+        <v>122.92</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-12-07-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-12-07-020.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 12 Instalaciones sanitarias</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Tanques, bombas e hidroneumáticos</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
